--- a/Elektroprosjekt-oversatt/Bestillingprosjekt_utfylt.xlsx
+++ b/Elektroprosjekt-oversatt/Bestillingprosjekt_utfylt.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -779,11 +779,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10 kohm resistor, 0805 (R2 trigger, R4 gate, R5 bleed)</t>
+          <t>10 kohm resistor, 0805 (R2 trigger, R4 gate pull-down)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
@@ -799,24 +799,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Farnell</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1454556</t>
+          <t>1997793</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10 ohm 0.5 W resistor, 0805 (gate drive R3)</t>
+          <t>10 kohm 0.4 W 1% resistor, through-hole (bleeder R_BLEED)</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>1.5</v>
@@ -834,12 +834,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1454664</t>
+          <t>1454556</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>820 ohm resistor, 0805 (12 V rail R9)</t>
+          <t>10 ohm 0.5 W resistor, 0805 (gate drive R3)</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,27 +859,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>Farnell</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>188-9651</t>
+          <t>1454664</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>100 ohm 2 W metal film resistor, through-hole (charge R_CHG)</t>
+          <t>820 ohm resistor, 0805 (12 V rail R9)</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="G18">
         <f>MAX(D18,E18)*F18</f>
@@ -894,12 +894,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>147-1981</t>
+          <t>188-9651</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.5 ohm 5 W wirewound resistor, through-hole (freewheel R_FW)</t>
+          <t>100 ohm 2 W metal film resistor, through-hole (charge R_CHG)</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -909,7 +909,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G19">
         <f>MAX(D19,E19)*F19</f>
@@ -924,12 +924,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>147-2264</t>
+          <t>147-1981</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.01 ohm 5 W wirewound shunt resistor (current sense R_SHUNT)</t>
+          <t>0.5 ohm 5 W wirewound resistor, through-hole (freewheel R_FW)</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -939,7 +939,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <f>MAX(D20,E20)*F20</f>
@@ -954,22 +954,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>187-2637</t>
+          <t>147-2264</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>470 uF 50 V low-ESR electrolytic capacitor, radial (C1+C2)</t>
+          <t>0.01 ohm 5 W wirewound shunt resistor (current sense R_SHUNT)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G21">
         <f>MAX(D21,E21)*F21</f>
@@ -984,22 +984,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>819-6715</t>
+          <t>187-2637</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SMBJ24A TVS diode, 24 V, unidirectional (supply clamp D4)</t>
+          <t>470 uF 50 V low-ESR electrolytic capacitor, radial (C1+C2)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G22">
         <f>MAX(D22,E22)*F22</f>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>178-4749</t>
+          <t>819-6715</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tact switch, 6x6 mm (fire button S1)</t>
+          <t>SMBJ24A TVS diode, 24 V, unidirectional (supply clamp D4)</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1029,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G23">
         <f>MAX(D23,E23)*F23</f>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>177-1896</t>
+          <t>178-4749</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Terminal block, 5.08 mm pitch, 2-pin PCB (supply input)</t>
+          <t>Tact switch, 6x6 mm (fire button S1)</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1059,7 +1059,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G24">
         <f>MAX(D24,E24)*F24</f>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>714-6726</t>
+          <t>177-1896</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pin header 2.54 mm (pickup output 2-pin + test points 6-pin)</t>
+          <t>Terminal block, 5.08 mm pitch, 2-pin PCB (supply input)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <f>MAX(D25,E25)*F25</f>
@@ -1104,22 +1104,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>173-5262</t>
+          <t>714-6726</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Magnet wire, 1.0 mm enamelled copper, 17 AWG, 10 m (transmitter coil)</t>
+          <t>Pin header 2.54 mm (pickup output 2-pin + test points 6-pin)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="G26">
         <f>MAX(D26,E26)*F26</f>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>173-5265</t>
+          <t>173-5262</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Magnet wire, 0.5 mm enamelled copper, 32 AWG, 10 m (pickup coil)</t>
+          <t>Magnet wire, 1.0 mm enamelled copper, 17 AWG, 10 m (transmitter coil)</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G27">
         <f>MAX(D27,E27)*F27</f>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>177-1103</t>
+          <t>173-5265</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plastic tubing 31 mm OD PVC (coil former, cut to ~20 mm)</t>
+          <t>Magnet wire, 0.5 mm enamelled copper, 32 AWG, 10 m (pickup coil)</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1179,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="G28">
         <f>MAX(D28,E28)*F28</f>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>190-4271</t>
+          <t>177-1103</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Standoffs, M3 x 6 mm, nylon (x4 under coil tube)</t>
+          <t>Plastic tubing 31 mm OD PVC (coil former, cut to ~20 mm)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G29">
         <f>MAX(D29,E29)*F29</f>
@@ -1219,27 +1219,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RS PCB service</t>
+          <t>190-4271</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PCB 80x80 mm, 2-layer, 35 um Cu, 1.6 mm FR-4, 5 pcs</t>
+          <t>Standoffs, M3 x 6 mm, nylon (x4 under coil tube)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>50</v>
+        <v>1.5</v>
       </c>
       <c r="G30">
         <f>MAX(D30,E30)*F30</f>
@@ -1249,85 +1249,116 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>RS PCB service</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PCB 80x80 mm, 2-layer, 35 um Cu, 1.6 mm FR-4, 5 pcs</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>50</v>
+      </c>
+      <c r="G31">
+        <f>MAX(D31,E31)*F31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>kommentarer (hvis noen)</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="G31" s="3">
-        <f>SUM(G6:G30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="D32" t="inlineStr">
+      <c r="G32" s="3">
+        <f>SUM(G6:G31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" t="inlineStr">
         <is>
           <t>+25%MVA</t>
         </is>
       </c>
-      <c r="G32">
-        <f>G31*0.25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="D33" s="3" t="inlineStr">
+      <c r="G33">
+        <f>G32*0.25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Totalsum</t>
         </is>
       </c>
-      <c r="G33" s="3">
-        <f>G31+G32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NOTES:</t>
-        </is>
-      </c>
-    </row>
+      <c r="G34" s="3">
+        <f>G32+G33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1. Part numbers are best-effort from catalog knowledge (no live site access in this session). Verify each row on no.farnell.com / no.rs-online.com</t>
+          <t>NOTES:</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">   before ordering; any in-stock part meeting the spec is acceptable per the assignment.</t>
+          <t>1. Part numbers are from the RS/Farnell catalog. Verify stock and price on no.farnell.com / no.rs-online.com</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2. Fallbacks: R_SHUNT 0.01 ohm -&gt; 2 x 0.02 ohm 5 W in series; 470 uF 50 V -&gt; any low-ESR type ESR &lt;= 25 mohm; 0.5 ohm -&gt; 0.47 ohm 5 W;</t>
+          <t xml:space="preserve">   before ordering; any in-stock part meeting the spec is acceptable per the assignment.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">   MUR1560 -&gt; MUR1520 (60 V is sufficient); IRF3707 -&gt; any 75 V N-ch TO-220 with Rds(on) &lt;= 1.6 mOhm @ 10 V; SMBJ24A -&gt; SMAJ24A.</t>
+          <t>2. Fallbacks: R_SHUNT 0.01 ohm -&gt; 2 x 0.02 ohm 5 W in series; 470 uF 50 V -&gt; any low-ESR type ESR &lt;= 25 mohm; 0.5 ohm -&gt; 0.47 ohm 5 W;</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3. Prices are NOK estimates ex. MVA; Sum column uses max(antall, min. kjop) x pr.stk, matching the template examples.</t>
+          <t xml:space="preserve">   MUR1560 -&gt; MUR1520 (60 V is sufficient); IRF3707 -&gt; any 30 V N-ch TO-220AB with Rds(on) &lt;= 1.6 mOhm @ 10 V; SMBJ24A -&gt; SMAJ24A.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
+        <is>
+          <t>3. Prices are NOK estimates ex. MVA; Sum column uses max(antall, min. kjop) x pr.stk, matching the template examples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>4. External lab equipment (not ordered): 24 V / 3 A bench PSU, oscilloscope &gt;= 100 MHz / 2 ch.</t>
         </is>
